--- a/annotators/team/tg/annotated/braunschweiger-zeitung.de.48722.xlsx
+++ b/annotators/team/tg/annotated/braunschweiger-zeitung.de.48722.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\in-progress\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\annotated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C034E809-B17E-4655-8A56-BA6D0EDA56D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0385CF46-68B9-41F7-900D-6F624ADA62D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9168" yWindow="0" windowWidth="13968" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sentence-level annotation" sheetId="1" r:id="rId1"/>
@@ -3781,7 +3781,7 @@
         <v>188</v>
       </c>
       <c r="E20" s="21" t="str">
-        <f t="shared" ref="E19:E29" si="5">IF(D20="?OLD","!!!","")</f>
+        <f t="shared" ref="E20:E29" si="5">IF(D20="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F20" s="22" t="str">
@@ -6464,7 +6464,7 @@
         <v>12</v>
       </c>
       <c r="E107" s="21" t="str">
-        <f t="shared" ref="E106:E139" si="13">IF(D107="?OLD","!!!","")</f>
+        <f t="shared" ref="E107:E139" si="13">IF(D107="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F107" s="22" t="str">
@@ -13481,7 +13481,7 @@
         <v>234</v>
       </c>
       <c r="E324" s="21" t="str">
-        <f t="shared" ref="E323:E333" si="33">IF(D324="?OLD","!!!","")</f>
+        <f t="shared" ref="E324:E333" si="33">IF(D324="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F324" s="22" t="str">
@@ -17163,7 +17163,7 @@
         <v>234</v>
       </c>
       <c r="E440" s="21" t="str">
-        <f t="shared" ref="E439:E445" si="44">IF(D440="?OLD","!!!","")</f>
+        <f t="shared" ref="E440:E445" si="44">IF(D440="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F440" s="22" t="str">
@@ -17175,7 +17175,7 @@
         <v/>
       </c>
       <c r="H440" s="24" t="str">
-        <f t="shared" ref="H439:H445" ca="1" si="45">IF(J440&lt;&gt;1,"",IF(I440="SBJ","CB","?"))</f>
+        <f t="shared" ref="H440:H445" ca="1" si="45">IF(J440&lt;&gt;1,"",IF(I440="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I440" s="25" t="str">
@@ -21677,7 +21677,7 @@
         <v>454</v>
       </c>
       <c r="E583" s="21" t="str">
-        <f t="shared" ref="E582:E592" si="62">IF(D583="?OLD","!!!","")</f>
+        <f t="shared" ref="E583:E592" si="62">IF(D583="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F583" s="22" t="str">
@@ -21689,7 +21689,7 @@
         <v/>
       </c>
       <c r="H583" s="24" t="str">
-        <f t="shared" ref="H582:H592" ca="1" si="63">IF(J583&lt;&gt;1,"",IF(I583="SBJ","CB","?"))</f>
+        <f t="shared" ref="H583:H592" ca="1" si="63">IF(J583&lt;&gt;1,"",IF(I583="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I583" s="25" t="str">
@@ -22083,7 +22083,7 @@
         <v>297</v>
       </c>
       <c r="E596" s="21" t="str">
-        <f t="shared" ref="E595:E609" si="64">IF(D596="?OLD","!!!","")</f>
+        <f t="shared" ref="E596:E609" si="64">IF(D596="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F596" s="22" t="str">
@@ -22095,7 +22095,7 @@
         <v/>
       </c>
       <c r="H596" s="24" t="str">
-        <f t="shared" ref="H595:H609" ca="1" si="65">IF(J596&lt;&gt;1,"",IF(I596="SBJ","CB","?"))</f>
+        <f t="shared" ref="H596:H609" ca="1" si="65">IF(J596&lt;&gt;1,"",IF(I596="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I596" s="25" t="str">
